--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_metropolitana.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_metropolitana.xlsx
@@ -394,10 +394,10 @@
         <v>12.40887064149904</v>
       </c>
       <c r="D2">
-        <v>72.86798185589727</v>
+        <v>72.86798185589726</v>
       </c>
       <c r="E2">
-        <v>14.7231475026037</v>
+        <v>14.72314750260369</v>
       </c>
     </row>
     <row r="3">
@@ -413,7 +413,7 @@
         <v>17.02890954410977</v>
       </c>
       <c r="D3">
-        <v>63.03724928366762</v>
+        <v>63.03724928366763</v>
       </c>
       <c r="E3">
         <v>19.93384117222261</v>
@@ -432,7 +432,7 @@
         <v>16.64831438551458</v>
       </c>
       <c r="D4">
-        <v>62.40820820966812</v>
+        <v>62.40820820966813</v>
       </c>
       <c r="E4">
         <v>20.94347740481729</v>
@@ -473,7 +473,7 @@
         <v>60.81192988619681</v>
       </c>
       <c r="E6">
-        <v>22.7324056763573</v>
+        <v>22.73240567635729</v>
       </c>
     </row>
     <row r="7">
@@ -489,7 +489,7 @@
         <v>16.59797633656718</v>
       </c>
       <c r="D7">
-        <v>65.70654564819746</v>
+        <v>65.70654564819745</v>
       </c>
       <c r="E7">
         <v>17.69547801523536</v>
@@ -546,10 +546,10 @@
         <v>15.23211630596398</v>
       </c>
       <c r="D10">
-        <v>63.56497993216781</v>
+        <v>63.56497993216782</v>
       </c>
       <c r="E10">
-        <v>21.2029037618682</v>
+        <v>21.20290376186821</v>
       </c>
     </row>
     <row r="11">
@@ -568,7 +568,7 @@
         <v>62.26614443815968</v>
       </c>
       <c r="E11">
-        <v>23.07259260840333</v>
+        <v>23.07259260840332</v>
       </c>
     </row>
     <row r="12">
@@ -622,7 +622,7 @@
         <v>14.58807292958263</v>
       </c>
       <c r="D14">
-        <v>60.26610025122106</v>
+        <v>60.26610025122107</v>
       </c>
       <c r="E14">
         <v>25.14582681919631</v>
@@ -644,7 +644,7 @@
         <v>62.28851525852527</v>
       </c>
       <c r="E15">
-        <v>25.09750698360828</v>
+        <v>25.09750698360829</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>148.5162143560816</v>
+        <v>148.5162143560815</v>
       </c>
       <c r="C20">
         <v>15.09775716777233</v>
@@ -755,7 +755,7 @@
         <v>12.27134723261818</v>
       </c>
       <c r="D21">
-        <v>65.9243248698519</v>
+        <v>65.92432486985189</v>
       </c>
       <c r="E21">
         <v>21.80432789752992</v>
@@ -774,7 +774,7 @@
         <v>15.25304705010918</v>
       </c>
       <c r="D22">
-        <v>58.7486652621858</v>
+        <v>58.74866526218579</v>
       </c>
       <c r="E22">
         <v>25.99828768770502</v>
@@ -828,7 +828,7 @@
         <v>113.8893973068375</v>
       </c>
       <c r="C25">
-        <v>17.21290078672115</v>
+        <v>17.21290078672116</v>
       </c>
       <c r="D25">
         <v>63.18343024825823</v>
@@ -926,7 +926,7 @@
         <v>15.02715925726173</v>
       </c>
       <c r="D30">
-        <v>61.45022729023808</v>
+        <v>61.45022729023807</v>
       </c>
       <c r="E30">
         <v>23.52261345250019</v>
@@ -967,7 +967,7 @@
         <v>61.77818088792763</v>
       </c>
       <c r="E32">
-        <v>22.60633968231819</v>
+        <v>22.6063396823182</v>
       </c>
     </row>
     <row r="33">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>140.2179937188251</v>
+        <v>140.217993718825</v>
       </c>
       <c r="C35">
         <v>14.31972699134944</v>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>58.77445734200489</v>
+        <v>58.77445734200488</v>
       </c>
       <c r="C37">
         <v>21.784823974605</v>
@@ -1075,10 +1075,10 @@
         <v>52.06934735967887</v>
       </c>
       <c r="C38">
-        <v>22.65479232976372</v>
+        <v>22.65479232976371</v>
       </c>
       <c r="D38">
-        <v>65.54900515843774</v>
+        <v>65.54900515843772</v>
       </c>
       <c r="E38">
         <v>11.79620251179855</v>
@@ -1091,16 +1091,16 @@
         </is>
       </c>
       <c r="B39">
-        <v>57.88968824940048</v>
+        <v>57.88968824940049</v>
       </c>
       <c r="C39">
         <v>21.6916354556804</v>
       </c>
       <c r="D39">
-        <v>65.75114440282979</v>
+        <v>65.75114440282981</v>
       </c>
       <c r="E39">
-        <v>12.5572201414898</v>
+        <v>12.55722014148981</v>
       </c>
     </row>
     <row r="40">
@@ -1151,7 +1151,7 @@
         <v>149.2476354256234</v>
       </c>
       <c r="C42">
-        <v>13.36820023563896</v>
+        <v>13.36820023563895</v>
       </c>
       <c r="D42">
         <v>66.68007701370729</v>
@@ -1176,7 +1176,7 @@
         <v>62.67138487374798</v>
       </c>
       <c r="E43">
-        <v>18.91561206741438</v>
+        <v>18.91561206741439</v>
       </c>
     </row>
     <row r="44">
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>127.4463007159904</v>
+        <v>127.4463007159905</v>
       </c>
       <c r="C47">
-        <v>17.62514271978847</v>
+        <v>17.62514271978848</v>
       </c>
       <c r="D47">
         <v>59.91226488792741</v>
@@ -1265,10 +1265,10 @@
         <v>125.5309534568459</v>
       </c>
       <c r="C48">
-        <v>18.77651450873918</v>
+        <v>18.77651450873919</v>
       </c>
       <c r="D48">
-        <v>57.65314780247751</v>
+        <v>57.65314780247752</v>
       </c>
       <c r="E48">
         <v>23.5703376887833</v>
@@ -1303,10 +1303,10 @@
         <v>106.9504896626768</v>
       </c>
       <c r="C50">
-        <v>18.18811538271239</v>
+        <v>18.18811538271238</v>
       </c>
       <c r="D50">
-        <v>62.35960615506407</v>
+        <v>62.35960615506406</v>
       </c>
       <c r="E50">
         <v>19.45227846222354</v>
@@ -1322,7 +1322,7 @@
         <v>112.0584988962472</v>
       </c>
       <c r="C51">
-        <v>17.29956798816144</v>
+        <v>17.29956798816145</v>
       </c>
       <c r="D51">
         <v>63.31479580876913</v>
@@ -1344,7 +1344,7 @@
         <v>19.46459577099636</v>
       </c>
       <c r="D52">
-        <v>64.93708821920414</v>
+        <v>64.93708821920416</v>
       </c>
       <c r="E52">
         <v>15.59831600979949</v>
